--- a/output/t_test_sugar_income.xlsx
+++ b/output/t_test_sugar_income.xlsx
@@ -14,13 +14,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
+    <t xml:space="preserve">Mean (≥300% poverty)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mean (&lt;300% poverty)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mean (≥300% poverty)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean difference</t>
+    <t xml:space="preserve">Mean difference (high - low)</t>
   </si>
   <si>
     <t xml:space="preserve">CI lower</t>
@@ -32,7 +32,7 @@
     <t xml:space="preserve">t statistic</t>
   </si>
   <si>
-    <t xml:space="preserve">p value</t>
+    <t xml:space="preserve">p value (one-sided)</t>
   </si>
 </sst>
 </file>
@@ -395,10 +395,10 @@
         <v>6.45</v>
       </c>
       <c r="D2" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E2" t="n">
-        <v>10.58</v>
+        <v>2.98</v>
+      </c>
+      <c r="E2" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F2" t="n">
         <v>3.06</v>
